--- a/Data/sge_data_for_qc/gene_cartoon_data/20260414_SGE_protein_domains.xlsx
+++ b/Data/sge_data_for_qc/gene_cartoon_data/20260414_SGE_protein_domains.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ivan/Documents/GitHub/PillarProject_CAVA_Analysis/Data/sge_data_for_qc/gene_cartoon_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E87A2E-E111-CD41-95A2-389EF9C0E061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7E97E9-6FB0-1B40-8B83-9B3F34699D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" activeTab="1" xr2:uid="{A6890493-859D-7C4F-828F-3AE6747E5755}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" activeTab="4" xr2:uid="{A6890493-859D-7C4F-828F-3AE6747E5755}"/>
   </bookViews>
   <sheets>
     <sheet name="BARD1" sheetId="1" r:id="rId1"/>
     <sheet name="RAD51D" sheetId="2" r:id="rId2"/>
+    <sheet name="XRCC2" sheetId="5" r:id="rId3"/>
+    <sheet name="CTCF" sheetId="3" r:id="rId4"/>
+    <sheet name="SFPQ" sheetId="4" r:id="rId5"/>
+    <sheet name="BRCA2" sheetId="6" r:id="rId6"/>
+    <sheet name="PALB2" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
   <si>
     <t>domain</t>
   </si>
@@ -61,16 +66,86 @@
   </si>
   <si>
     <t>RecA</t>
+  </si>
+  <si>
+    <t>ZF1</t>
+  </si>
+  <si>
+    <t>ZF2</t>
+  </si>
+  <si>
+    <t>ZF3</t>
+  </si>
+  <si>
+    <t>ZF4</t>
+  </si>
+  <si>
+    <t>ZF5</t>
+  </si>
+  <si>
+    <t>ZF6</t>
+  </si>
+  <si>
+    <t>ZF7</t>
+  </si>
+  <si>
+    <t>ZF8</t>
+  </si>
+  <si>
+    <t>ZF9</t>
+  </si>
+  <si>
+    <t>ZF10</t>
+  </si>
+  <si>
+    <t>ZF11</t>
+  </si>
+  <si>
+    <t>NCR</t>
+  </si>
+  <si>
+    <t>KTYQR</t>
+  </si>
+  <si>
+    <t>YDF</t>
+  </si>
+  <si>
+    <t>BRC Repeats</t>
+  </si>
+  <si>
+    <t>DNA-Binding</t>
+  </si>
+  <si>
+    <t>Transactivation</t>
+  </si>
+  <si>
+    <t>NLS</t>
+  </si>
+  <si>
+    <t>Coiled-Coil</t>
+  </si>
+  <si>
+    <t>ChAM Motif</t>
+  </si>
+  <si>
+    <t>WD-40</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -96,8 +171,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -525,4 +601,351 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3804F04-A124-6649-9683-FE9A858310A9}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>42</v>
+      </c>
+      <c r="C2">
+        <v>280</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4706ACF9-F1DD-0F42-A489-93E6C24E5AEF}">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2">
+        <v>23</v>
+      </c>
+      <c r="C2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3">
+        <v>226</v>
+      </c>
+      <c r="C3">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>266</v>
+      </c>
+      <c r="C4">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>294</v>
+      </c>
+      <c r="C5">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>322</v>
+      </c>
+      <c r="C6">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>351</v>
+      </c>
+      <c r="C7">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>379</v>
+      </c>
+      <c r="C8">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>407</v>
+      </c>
+      <c r="C9">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <v>437</v>
+      </c>
+      <c r="C10">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <v>467</v>
+      </c>
+      <c r="C11">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12">
+        <v>495</v>
+      </c>
+      <c r="C12">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13">
+        <v>523</v>
+      </c>
+      <c r="C13">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14">
+        <v>555</v>
+      </c>
+      <c r="C14">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1">
+        <v>612</v>
+      </c>
+      <c r="C15">
+        <v>637</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C754F2-3F43-454A-B00A-EF6FF3B03B24}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB7B95-3023-8F4B-9B3B-2F71FF63D158}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2">
+        <v>26</v>
+      </c>
+      <c r="C2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3">
+        <v>1002</v>
+      </c>
+      <c r="C3">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4">
+        <v>2482</v>
+      </c>
+      <c r="C4">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5">
+        <v>3263</v>
+      </c>
+      <c r="C5">
+        <v>3385</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AEF27BF-D775-4F4E-8551-D5E7BCF61AE7}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3">
+        <v>395</v>
+      </c>
+      <c r="C3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4">
+        <v>859</v>
+      </c>
+      <c r="C4">
+        <v>1186</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Data/sge_data_for_qc/gene_cartoon_data/20260414_SGE_protein_domains.xlsx
+++ b/Data/sge_data_for_qc/gene_cartoon_data/20260414_SGE_protein_domains.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ivan/Documents/GitHub/PillarProject_CAVA_Analysis/Data/sge_data_for_qc/gene_cartoon_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7E97E9-6FB0-1B40-8B83-9B3F34699D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305CF0FE-0B77-0C48-829C-FF8406F88DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" activeTab="4" xr2:uid="{A6890493-859D-7C4F-828F-3AE6747E5755}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
   <si>
     <t>domain</t>
   </si>
@@ -68,48 +68,9 @@
     <t>RecA</t>
   </si>
   <si>
-    <t>ZF1</t>
-  </si>
-  <si>
-    <t>ZF2</t>
-  </si>
-  <si>
-    <t>ZF3</t>
-  </si>
-  <si>
-    <t>ZF4</t>
-  </si>
-  <si>
-    <t>ZF5</t>
-  </si>
-  <si>
-    <t>ZF6</t>
-  </si>
-  <si>
-    <t>ZF7</t>
-  </si>
-  <si>
-    <t>ZF8</t>
-  </si>
-  <si>
-    <t>ZF9</t>
-  </si>
-  <si>
-    <t>ZF10</t>
-  </si>
-  <si>
-    <t>ZF11</t>
-  </si>
-  <si>
     <t>NCR</t>
   </si>
   <si>
-    <t>KTYQR</t>
-  </si>
-  <si>
-    <t>YDF</t>
-  </si>
-  <si>
     <t>BRC Repeats</t>
   </si>
   <si>
@@ -129,6 +90,18 @@
   </si>
   <si>
     <t>WD-40</t>
+  </si>
+  <si>
+    <t>Zinc Fingers</t>
+  </si>
+  <si>
+    <t>RRM2</t>
+  </si>
+  <si>
+    <t>RRM1</t>
+  </si>
+  <si>
+    <t>NOPS</t>
   </si>
 </sst>
 </file>
@@ -637,7 +610,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4706ACF9-F1DD-0F42-A489-93E6C24E5AEF}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -653,155 +626,23 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B2">
-        <v>23</v>
+        <v>266</v>
       </c>
       <c r="C2">
-        <v>27</v>
+        <v>577</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3">
-        <v>226</v>
+        <v>8</v>
+      </c>
+      <c r="B3" s="1">
+        <v>612</v>
       </c>
       <c r="C3">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>266</v>
-      </c>
-      <c r="C4">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>294</v>
-      </c>
-      <c r="C5">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>322</v>
-      </c>
-      <c r="C6">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7">
-        <v>351</v>
-      </c>
-      <c r="C7">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8">
-        <v>379</v>
-      </c>
-      <c r="C8">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9">
-        <v>407</v>
-      </c>
-      <c r="C9">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10">
-        <v>437</v>
-      </c>
-      <c r="C10">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11">
-        <v>467</v>
-      </c>
-      <c r="C11">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12">
-        <v>495</v>
-      </c>
-      <c r="C12">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13">
-        <v>523</v>
-      </c>
-      <c r="C13">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14">
-        <v>555</v>
-      </c>
-      <c r="C14">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="1">
-        <v>612</v>
-      </c>
-      <c r="C15">
         <v>637</v>
       </c>
     </row>
@@ -812,7 +653,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C754F2-3F43-454A-B00A-EF6FF3B03B24}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -824,6 +665,50 @@
       </c>
       <c r="C1" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2">
+        <v>299</v>
+      </c>
+      <c r="C2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>370</v>
+      </c>
+      <c r="C3">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>450</v>
+      </c>
+      <c r="C4">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>499</v>
+      </c>
+      <c r="C5">
+        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -849,7 +734,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>26</v>
@@ -860,7 +745,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>1002</v>
@@ -871,7 +756,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>2482</v>
@@ -882,7 +767,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B5">
         <v>3263</v>
@@ -914,7 +799,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>9</v>
@@ -925,7 +810,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>395</v>
@@ -936,7 +821,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>859</v>
